--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_guide_new/lang_guide_new__name_title__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_guide_new/lang_guide_new__name_title__part_0001.xlsx
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Audio Casket</t>
+          <t>Hộp Âm Thanh</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Chạm to select the weapon</t>
+          <t>Chạm to select the vũ khí</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Chạm to switch weapon</t>
+          <t>Chạm to switch vũ khí</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Chạm to select the weapon</t>
+          <t>Chạm to select the vũ khí</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Chạm to switch weapon</t>
+          <t>Chạm to switch vũ khí</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
